--- a/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>GIL</t>
   </si>
@@ -656,198 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43828</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42736</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42372</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42281</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41917</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41546</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41182</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3195900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3240500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2922600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1981300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2823900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2908600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2750800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2585100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2959200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2415500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2360000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2184300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1948300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2341800</v>
+      </c>
+      <c r="E9" s="3">
         <v>2274000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2046700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1741800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2119400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2102600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1949600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1865400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2229100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1830100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1701300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1550300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1552100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>854200</v>
+      </c>
+      <c r="E10" s="3">
         <v>966500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>875900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>239500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>704500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>806000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>801200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>719700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>730100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>585300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>658700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>634000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>396100</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,9 +919,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,51 +964,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-95100</v>
+      </c>
+      <c r="E14" s="3">
         <v>39000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-90200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>148000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>47300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>21800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15100</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,9 +1054,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1073,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2552100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2637100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2270700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2162100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2534900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2505400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2349800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2213500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2632000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2158900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1990600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1841600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1793100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>643900</v>
+      </c>
+      <c r="E18" s="3">
         <v>603400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>651900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-180800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>289000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>403200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>401000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>371500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>327200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>256600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>369400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>342700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>155100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,218 +1182,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-15100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-7100</v>
       </c>
       <c r="J20" s="3">
         <v>-7100</v>
       </c>
       <c r="K20" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-9100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>742600</v>
+      </c>
+      <c r="E21" s="3">
         <v>720100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>777500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-48800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>438400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>555000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>556100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>505000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>464500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>364500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>464200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>429900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>246000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E22" s="3">
         <v>28700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>564200</v>
+      </c>
+      <c r="E23" s="3">
         <v>566400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>624600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-229400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>249800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>372100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>376800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>351800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>309400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>241200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>366500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>330700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>144100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E24" s="3">
         <v>24900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1449,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>533600</v>
+      </c>
+      <c r="E26" s="3">
         <v>541500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>607200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-225300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>259800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>350800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>362300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>346600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>304900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>237300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>359600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>320200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>148500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>533600</v>
+      </c>
+      <c r="E27" s="3">
         <v>541500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>607200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-225300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>259800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>350800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>362300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>346600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>304900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>237300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>359600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>320200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>148500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1584,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1568,9 +1629,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1674,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1719,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E32" s="3">
         <v>8200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>15100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>7100</v>
       </c>
       <c r="J32" s="3">
         <v>7100</v>
       </c>
       <c r="K32" s="3">
+        <v>7100</v>
+      </c>
+      <c r="L32" s="3">
         <v>9100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>533600</v>
+      </c>
+      <c r="E33" s="3">
         <v>541500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>607200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-225300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>259800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>350800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>362300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>346600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>304900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>237300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>359600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>320200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>148500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1854,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>533600</v>
+      </c>
+      <c r="E35" s="3">
         <v>541500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>607200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-225300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>259800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>350800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>362300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>346600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>304900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>237300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>359600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>320200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>148500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43828</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42736</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42372</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42281</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41917</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41546</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41182</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1971,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,76 +1990,80 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E41" s="3">
         <v>150400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>179200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>505300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>50700</v>
-      </c>
-      <c r="L41" s="3">
-        <v>65100</v>
       </c>
       <c r="M41" s="3">
         <v>65100</v>
       </c>
       <c r="N41" s="3">
+        <v>65100</v>
+      </c>
+      <c r="O41" s="3">
         <v>96500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>68700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E42" s="3">
         <v>48300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>70000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>88800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>46000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>39800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22700</v>
-      </c>
-      <c r="K42" s="3">
-        <v>100</v>
       </c>
       <c r="L42" s="3">
         <v>100</v>
@@ -1982,202 +2072,217 @@
         <v>100</v>
       </c>
       <c r="N42" s="3">
+        <v>100</v>
+      </c>
+      <c r="O42" s="3">
         <v>900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1700</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>412500</v>
+      </c>
+      <c r="E43" s="3">
         <v>248800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>330000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>201100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>320900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>318800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>247300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>277700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>306100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>355700</v>
       </c>
       <c r="M43" s="3">
         <v>355700</v>
       </c>
       <c r="N43" s="3">
+        <v>355700</v>
+      </c>
+      <c r="O43" s="3">
         <v>255700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>257900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1089400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1225900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>774400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>728000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1052100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>940000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>945700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>954900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>851000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>779400</v>
       </c>
       <c r="M44" s="3">
         <v>779400</v>
       </c>
       <c r="N44" s="3">
+        <v>779400</v>
+      </c>
+      <c r="O44" s="3">
         <v>595800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>553100</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E45" s="3">
         <v>53500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>93700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>47000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>88400</v>
       </c>
       <c r="M45" s="3">
         <v>88400</v>
       </c>
       <c r="N45" s="3">
+        <v>88400</v>
+      </c>
+      <c r="O45" s="3">
         <v>31800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39200</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1687500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1727000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1447200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1544500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1514200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1382900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1307900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1340500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1253600</v>
-      </c>
-      <c r="L46" s="3">
-        <v>1247400</v>
       </c>
       <c r="M46" s="3">
         <v>1247400</v>
       </c>
       <c r="N46" s="3">
+        <v>1247400</v>
+      </c>
+      <c r="O46" s="3">
         <v>980700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>912600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2800</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -2191,99 +2296,108 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>12100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1256000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1193100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1077500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>956200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1068500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>990500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1035800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1076900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1044400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>873700</v>
       </c>
       <c r="M48" s="3">
         <v>873700</v>
       </c>
       <c r="N48" s="3">
+        <v>873700</v>
+      </c>
+      <c r="O48" s="3">
         <v>655900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>194200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>533100</v>
+      </c>
+      <c r="E49" s="3">
         <v>501600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>590400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>496500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>611700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>620900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>628200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>556300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>527400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>463800</v>
       </c>
       <c r="M49" s="3">
         <v>463800</v>
       </c>
       <c r="N49" s="3">
+        <v>463800</v>
+      </c>
+      <c r="O49" s="3">
         <v>397600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>480900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2437,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,51 +2482,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E52" s="3">
         <v>18400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>8100</v>
       </c>
       <c r="M52" s="3">
         <v>8100</v>
       </c>
       <c r="N52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="O52" s="3">
         <v>9400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18800</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2572,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3514900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3440200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3136700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3020900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3211100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3004600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2980700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2990100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2834300</v>
-      </c>
-      <c r="L54" s="3">
-        <v>2593000</v>
       </c>
       <c r="M54" s="3">
         <v>2593000</v>
       </c>
       <c r="N54" s="3">
+        <v>2593000</v>
+      </c>
+      <c r="O54" s="3">
         <v>2043700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1896400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2639,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,67 +2658,71 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>403500</v>
+      </c>
+      <c r="E57" s="3">
         <v>462500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>436100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>326100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>395600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>332500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>255800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>232500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>230700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>736000</v>
       </c>
       <c r="M57" s="3">
         <v>736000</v>
       </c>
       <c r="N57" s="3">
+        <v>736000</v>
+      </c>
+      <c r="O57" s="3">
         <v>289400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>256400</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>314200</v>
+      </c>
+      <c r="E58" s="3">
         <v>163800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14500</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
@@ -2605,183 +2739,198 @@
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E59" s="3">
         <v>15300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>7300</v>
       </c>
       <c r="M59" s="3">
         <v>7300</v>
       </c>
-      <c r="N59" s="3" t="s">
+      <c r="N59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>724100</v>
+      </c>
+      <c r="E60" s="3">
         <v>641700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>463600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>359600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>422400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>347000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>258500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>235900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>233200</v>
-      </c>
-      <c r="L60" s="3">
-        <v>368700</v>
       </c>
       <c r="M60" s="3">
         <v>368700</v>
       </c>
       <c r="N60" s="3">
+        <v>368700</v>
+      </c>
+      <c r="O60" s="3">
         <v>289400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>256400</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>768900</v>
+      </c>
+      <c r="E61" s="3">
         <v>860200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>693800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1066600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>912000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>669000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>630000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>600000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>375000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>157000</v>
       </c>
       <c r="M61" s="3">
         <v>157000</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>181000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E62" s="3">
         <v>56200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>59900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>35900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>42200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>52500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>43800</v>
       </c>
       <c r="M62" s="3">
         <v>43800</v>
       </c>
       <c r="N62" s="3">
+        <v>43800</v>
+      </c>
+      <c r="O62" s="3">
         <v>34800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2970,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3015,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3060,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1557400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1558100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1217300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1462100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1376600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1068500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>929300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>870500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>645800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>569500</v>
       </c>
       <c r="M66" s="3">
         <v>569500</v>
       </c>
       <c r="N66" s="3">
+        <v>569500</v>
+      </c>
+      <c r="O66" s="3">
         <v>324200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>470100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3127,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3169,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3214,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3259,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3304,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1611200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1590500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1604700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1359100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1628000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1740300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1853500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1903500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2022800</v>
-      </c>
-      <c r="L72" s="3">
-        <v>1885900</v>
       </c>
       <c r="M72" s="3">
         <v>1885900</v>
       </c>
       <c r="N72" s="3">
+        <v>1885900</v>
+      </c>
+      <c r="O72" s="3">
         <v>1583300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1306700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3394,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3439,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3484,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1957500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1882200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1919400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1558900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1834500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1936100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2051400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2119600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2188400</v>
-      </c>
-      <c r="L76" s="3">
-        <v>2023500</v>
       </c>
       <c r="M76" s="3">
         <v>2023500</v>
       </c>
       <c r="N76" s="3">
+        <v>2023500</v>
+      </c>
+      <c r="O76" s="3">
         <v>1719400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1426300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3574,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43828</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42736</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42372</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42281</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41917</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41546</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41182</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>533600</v>
+      </c>
+      <c r="E81" s="3">
         <v>541500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>607200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-225300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>259800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>350800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>362300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>346600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>304900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>237300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>359600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>320200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>148500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3691,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E83" s="3">
         <v>124900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>135400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>147200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>156800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>158100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>162200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>140600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>146400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>116600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>95600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>95300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>94600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3778,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3823,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3868,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3913,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3958,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>546600</v>
+      </c>
+      <c r="E89" s="3">
         <v>413500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>617500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>415000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>361000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>538500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>613400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>537900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>353600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>219800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>264100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>427200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>219600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4025,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-203300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-239100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-127500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-50700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-128700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-107700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-92000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-129400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-319400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-284000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-286600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-162600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-76800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4112,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4157,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-154900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-182400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-187800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-135800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-110900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-210000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-303400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-425300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-390700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-389500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-172100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-162000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,50 +4224,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-131800</v>
+      </c>
+      <c r="E96" s="3">
         <v>-123800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-90500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-30600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-110300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-94600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-84800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-74400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-79700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-63700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-53200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-43700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-36600</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4311,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4356,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,133 +4401,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-452800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-258300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-754800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>83500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-207800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-433200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-389300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-246300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>59400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>154800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>93700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-228300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-69100</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-60800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-326000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>441100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-32200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>GIL</t>
   </si>
@@ -700,7 +700,7 @@
         <v>43828</v>
       </c>
       <c r="I7" s="2">
-        <v>43465</v>
+        <v>43464</v>
       </c>
       <c r="J7" s="2">
         <v>43100</v>
@@ -775,19 +775,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2341800</v>
+        <v>2315900</v>
       </c>
       <c r="E9" s="3">
-        <v>2274000</v>
+        <v>2281000</v>
       </c>
       <c r="F9" s="3">
-        <v>2046700</v>
+        <v>2092400</v>
       </c>
       <c r="G9" s="3">
-        <v>1741800</v>
+        <v>1788000</v>
       </c>
       <c r="H9" s="3">
-        <v>2119400</v>
+        <v>2083400</v>
       </c>
       <c r="I9" s="3">
         <v>2102600</v>
@@ -820,19 +820,19 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>854200</v>
+        <v>880100</v>
       </c>
       <c r="E10" s="3">
-        <v>966500</v>
+        <v>959500</v>
       </c>
       <c r="F10" s="3">
-        <v>875900</v>
+        <v>830200</v>
       </c>
       <c r="G10" s="3">
-        <v>239500</v>
+        <v>193300</v>
       </c>
       <c r="H10" s="3">
-        <v>704500</v>
+        <v>740500</v>
       </c>
       <c r="I10" s="3">
         <v>806000</v>
@@ -974,25 +974,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-95100</v>
+        <v>-94200</v>
       </c>
       <c r="E14" s="3">
-        <v>39000</v>
+        <v>29900</v>
       </c>
       <c r="F14" s="3">
-        <v>-90200</v>
+        <v>-133200</v>
       </c>
       <c r="G14" s="3">
-        <v>148000</v>
+        <v>86300</v>
       </c>
       <c r="H14" s="3">
-        <v>47300</v>
+        <v>83300</v>
       </c>
       <c r="I14" s="3">
-        <v>21800</v>
+        <v>34200</v>
       </c>
       <c r="J14" s="3">
-        <v>22000</v>
+        <v>22900</v>
       </c>
       <c r="K14" s="3">
         <v>10000</v>
@@ -1019,25 +1019,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>102700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>104800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>116200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>126400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>138300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>153600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>157300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,25 +1080,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2552100</v>
+        <v>2646200</v>
       </c>
       <c r="E17" s="3">
-        <v>2637100</v>
+        <v>2607200</v>
       </c>
       <c r="F17" s="3">
-        <v>2270700</v>
+        <v>2403900</v>
       </c>
       <c r="G17" s="3">
-        <v>2162100</v>
+        <v>2075800</v>
       </c>
       <c r="H17" s="3">
-        <v>2534900</v>
+        <v>2451600</v>
       </c>
       <c r="I17" s="3">
-        <v>2505400</v>
+        <v>2471200</v>
       </c>
       <c r="J17" s="3">
-        <v>2349800</v>
+        <v>2326900</v>
       </c>
       <c r="K17" s="3">
         <v>2213500</v>
@@ -1125,25 +1125,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>643900</v>
+        <v>549700</v>
       </c>
       <c r="E18" s="3">
-        <v>603400</v>
+        <v>633300</v>
       </c>
       <c r="F18" s="3">
-        <v>651900</v>
+        <v>518700</v>
       </c>
       <c r="G18" s="3">
-        <v>-180800</v>
+        <v>-94500</v>
       </c>
       <c r="H18" s="3">
-        <v>289000</v>
+        <v>372300</v>
       </c>
       <c r="I18" s="3">
-        <v>403200</v>
+        <v>437400</v>
       </c>
       <c r="J18" s="3">
-        <v>401000</v>
+        <v>423900</v>
       </c>
       <c r="K18" s="3">
         <v>371500</v>
@@ -1189,25 +1189,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-22900</v>
+        <v>22500</v>
       </c>
       <c r="E20" s="3">
-        <v>-8200</v>
+        <v>8200</v>
       </c>
       <c r="F20" s="3">
-        <v>-9800</v>
+        <v>9600</v>
       </c>
       <c r="G20" s="3">
-        <v>-15100</v>
+        <v>14900</v>
       </c>
       <c r="H20" s="3">
-        <v>-7400</v>
+        <v>7100</v>
       </c>
       <c r="I20" s="3">
-        <v>-6300</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="3">
-        <v>-7100</v>
+        <v>6700</v>
       </c>
       <c r="K20" s="3">
         <v>-7100</v>
@@ -1234,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>742600</v>
+        <v>629900</v>
       </c>
       <c r="E21" s="3">
-        <v>720100</v>
+        <v>729800</v>
       </c>
       <c r="F21" s="3">
-        <v>777500</v>
+        <v>625200</v>
       </c>
       <c r="G21" s="3">
-        <v>-48800</v>
+        <v>17100</v>
       </c>
       <c r="H21" s="3">
-        <v>438400</v>
+        <v>503500</v>
       </c>
       <c r="I21" s="3">
-        <v>555000</v>
+        <v>585000</v>
       </c>
       <c r="J21" s="3">
-        <v>556100</v>
+        <v>574500</v>
       </c>
       <c r="K21" s="3">
         <v>505000</v>
@@ -1279,25 +1279,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>56800</v>
+        <v>57200</v>
       </c>
       <c r="E22" s="3">
-        <v>28700</v>
+        <v>28800</v>
       </c>
       <c r="F22" s="3">
-        <v>17600</v>
+        <v>17700</v>
       </c>
       <c r="G22" s="3">
-        <v>33400</v>
+        <v>33700</v>
       </c>
       <c r="H22" s="3">
-        <v>31800</v>
+        <v>32100</v>
       </c>
       <c r="I22" s="3">
-        <v>24800</v>
+        <v>25100</v>
       </c>
       <c r="J22" s="3">
-        <v>17100</v>
+        <v>17400</v>
       </c>
       <c r="K22" s="3">
         <v>12600</v>
@@ -1729,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>22900</v>
+        <v>-22500</v>
       </c>
       <c r="E32" s="3">
-        <v>8200</v>
+        <v>-8200</v>
       </c>
       <c r="F32" s="3">
-        <v>9800</v>
+        <v>-9600</v>
       </c>
       <c r="G32" s="3">
-        <v>15100</v>
+        <v>-14900</v>
       </c>
       <c r="H32" s="3">
-        <v>7400</v>
+        <v>-7100</v>
       </c>
       <c r="I32" s="3">
-        <v>6300</v>
+        <v>-6000</v>
       </c>
       <c r="J32" s="3">
-        <v>7100</v>
+        <v>-6700</v>
       </c>
       <c r="K32" s="3">
         <v>7100</v>
@@ -1929,7 +1929,7 @@
         <v>43828</v>
       </c>
       <c r="I38" s="2">
-        <v>43465</v>
+        <v>43464</v>
       </c>
       <c r="J38" s="2">
         <v>43100</v>
@@ -2054,13 +2054,13 @@
         <v>88800</v>
       </c>
       <c r="H42" s="3">
-        <v>46000</v>
+        <v>49600</v>
       </c>
       <c r="I42" s="3">
-        <v>39800</v>
+        <v>52700</v>
       </c>
       <c r="J42" s="3">
-        <v>29900</v>
+        <v>28700</v>
       </c>
       <c r="K42" s="3">
         <v>22700</v>
@@ -2177,25 +2177,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>50800</v>
+        <v>15800</v>
       </c>
       <c r="E45" s="3">
-        <v>53500</v>
+        <v>23800</v>
       </c>
       <c r="F45" s="3">
-        <v>93700</v>
+        <v>62800</v>
       </c>
       <c r="G45" s="3">
-        <v>21300</v>
+        <v>4900</v>
       </c>
       <c r="H45" s="3">
-        <v>31100</v>
+        <v>6100</v>
       </c>
       <c r="I45" s="3">
-        <v>37600</v>
+        <v>4800</v>
       </c>
       <c r="J45" s="3">
-        <v>32100</v>
+        <v>16900</v>
       </c>
       <c r="K45" s="3">
         <v>47000</v>
@@ -2266,23 +2266,23 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>12900</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2800</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -2492,22 +2492,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25400</v>
+        <v>14300</v>
       </c>
       <c r="E52" s="3">
-        <v>18400</v>
+        <v>2500</v>
       </c>
       <c r="F52" s="3">
-        <v>21100</v>
+        <v>3800</v>
       </c>
       <c r="G52" s="3">
-        <v>22300</v>
+        <v>6000</v>
       </c>
       <c r="H52" s="3">
-        <v>13700</v>
+        <v>6700</v>
       </c>
       <c r="I52" s="3">
-        <v>7500</v>
+        <v>10300</v>
       </c>
       <c r="J52" s="3">
         <v>8800</v>
@@ -2665,25 +2665,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>403500</v>
+        <v>323400</v>
       </c>
       <c r="E57" s="3">
-        <v>462500</v>
+        <v>380600</v>
       </c>
       <c r="F57" s="3">
-        <v>436100</v>
+        <v>355900</v>
       </c>
       <c r="G57" s="3">
-        <v>326100</v>
+        <v>289900</v>
       </c>
       <c r="H57" s="3">
-        <v>395600</v>
+        <v>348300</v>
       </c>
       <c r="I57" s="3">
-        <v>332500</v>
+        <v>290900</v>
       </c>
       <c r="J57" s="3">
-        <v>255800</v>
+        <v>246400</v>
       </c>
       <c r="K57" s="3">
         <v>232500</v>
@@ -2710,25 +2710,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>314200</v>
+        <v>326700</v>
       </c>
       <c r="E58" s="3">
-        <v>163800</v>
+        <v>190700</v>
       </c>
       <c r="F58" s="3">
-        <v>15300</v>
+        <v>29400</v>
       </c>
       <c r="G58" s="3">
-        <v>15900</v>
+        <v>54400</v>
       </c>
       <c r="H58" s="3">
-        <v>14500</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>56200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -2755,22 +2755,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6400</v>
+        <v>60200</v>
       </c>
       <c r="E59" s="3">
-        <v>15300</v>
+        <v>59700</v>
       </c>
       <c r="F59" s="3">
-        <v>12200</v>
+        <v>64800</v>
       </c>
       <c r="G59" s="3">
-        <v>17700</v>
+        <v>6700</v>
       </c>
       <c r="H59" s="3">
-        <v>12300</v>
+        <v>10300</v>
       </c>
       <c r="I59" s="3">
-        <v>14400</v>
+        <v>13900</v>
       </c>
       <c r="J59" s="3">
         <v>2600</v>
@@ -2890,25 +2890,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>64400</v>
+        <v>11100</v>
       </c>
       <c r="E62" s="3">
-        <v>56200</v>
+        <v>10700</v>
       </c>
       <c r="F62" s="3">
-        <v>59900</v>
+        <v>13200</v>
       </c>
       <c r="G62" s="3">
-        <v>35900</v>
+        <v>12200</v>
       </c>
       <c r="H62" s="3">
-        <v>42200</v>
+        <v>10800</v>
       </c>
       <c r="I62" s="3">
-        <v>52500</v>
+        <v>14300</v>
       </c>
       <c r="J62" s="3">
-        <v>40900</v>
+        <v>17800</v>
       </c>
       <c r="K62" s="3">
         <v>34600</v>
@@ -3604,7 +3604,7 @@
         <v>43828</v>
       </c>
       <c r="I80" s="2">
-        <v>43465</v>
+        <v>43464</v>
       </c>
       <c r="J80" s="2">
         <v>43100</v>
@@ -3698,25 +3698,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>121600</v>
+        <v>107800</v>
       </c>
       <c r="E83" s="3">
-        <v>124900</v>
+        <v>105800</v>
       </c>
       <c r="F83" s="3">
-        <v>135400</v>
+        <v>117300</v>
       </c>
       <c r="G83" s="3">
-        <v>147200</v>
+        <v>126800</v>
       </c>
       <c r="H83" s="3">
-        <v>156800</v>
+        <v>134300</v>
       </c>
       <c r="I83" s="3">
-        <v>158100</v>
+        <v>130700</v>
       </c>
       <c r="J83" s="3">
-        <v>162200</v>
+        <v>136600</v>
       </c>
       <c r="K83" s="3">
         <v>140600</v>
@@ -4231,25 +4231,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-131800</v>
+        <v>131800</v>
       </c>
       <c r="E96" s="3">
-        <v>-123800</v>
+        <v>123800</v>
       </c>
       <c r="F96" s="3">
-        <v>-90500</v>
+        <v>90500</v>
       </c>
       <c r="G96" s="3">
-        <v>-30600</v>
+        <v>30600</v>
       </c>
       <c r="H96" s="3">
-        <v>-110300</v>
+        <v>110300</v>
       </c>
       <c r="I96" s="3">
-        <v>-94600</v>
+        <v>94600</v>
       </c>
       <c r="J96" s="3">
-        <v>-84800</v>
+        <v>84800</v>
       </c>
       <c r="K96" s="3">
         <v>-74400</v>

--- a/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>GIL</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43828</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43464</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42736</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42372</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42281</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41917</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41546</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41182</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3270600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3195900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3240500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2922600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1981300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2823900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2908600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2750800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2585100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2959200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2415500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2360000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2184300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1948300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2315900</v>
+        <v>2266900</v>
       </c>
       <c r="E9" s="3">
+        <v>2319000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2281000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2092400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1788000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2083400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2102600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1949600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1865400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2229100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1830100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1701300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1550300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1552100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>880100</v>
+        <v>1003700</v>
       </c>
       <c r="E10" s="3">
+        <v>877000</v>
+      </c>
+      <c r="F10" s="3">
         <v>959500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>830200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>193300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>740500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>806000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>801200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>719700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>730100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>585300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>658700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>634000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>396100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,9 +935,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,81 +983,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-94200</v>
+        <v>77400</v>
       </c>
       <c r="E14" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="F14" s="3">
         <v>29900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-133200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>86300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>83300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>34200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15100</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E15" s="3">
         <v>102700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>104800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>116200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>126400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>138300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>153600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>157300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1057,9 +1079,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2646200</v>
+        <v>2575000</v>
       </c>
       <c r="E17" s="3">
+        <v>2643000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2607200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2403900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2075800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2451600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2471200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2326900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2213500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2632000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2158900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1990600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1841600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1793100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>549700</v>
+        <v>695600</v>
       </c>
       <c r="E18" s="3">
+        <v>552900</v>
+      </c>
+      <c r="F18" s="3">
         <v>633300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>518700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-94500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>372300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>437400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>423900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>371500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>327200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>256600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>369400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>342700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>155100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,233 +1215,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E20" s="3">
         <v>22500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>629900</v>
+        <v>795800</v>
       </c>
       <c r="E21" s="3">
+        <v>633100</v>
+      </c>
+      <c r="F21" s="3">
         <v>729800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>625200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>503500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>585000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>574500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>505000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>464500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>364500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>464200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>429900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>246000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E22" s="3">
         <v>57200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>32100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7300</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>514100</v>
+      </c>
+      <c r="E23" s="3">
         <v>564200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>566400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>624600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-229400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>249800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>372100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>376800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>351800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>309400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>241200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>366500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>330700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>144100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E24" s="3">
         <v>30600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E26" s="3">
         <v>533600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>541500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>607200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-225300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>259800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>350800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>362300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>346600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>304900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>237300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>359600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>320200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>148500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E27" s="3">
         <v>533600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>541500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>607200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-225300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>259800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>350800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>362300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>346600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>304900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>237300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>359600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>320200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>148500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,9 +1644,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1632,9 +1692,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3700</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E33" s="3">
         <v>533600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>541500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>607200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-225300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>259800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>350800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>362300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>346600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>304900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>237300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>359600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>320200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>148500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E35" s="3">
         <v>533600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>541500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>607200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-225300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>259800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>350800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>362300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>346600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>304900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>237300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>359600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>320200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>148500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43828</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43464</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42736</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42372</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42281</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41917</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41546</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41182</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,82 +2076,86 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E41" s="3">
         <v>89600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>150400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>179200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>505300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50700</v>
-      </c>
-      <c r="M41" s="3">
-        <v>65100</v>
       </c>
       <c r="N41" s="3">
         <v>65100</v>
       </c>
       <c r="O41" s="3">
+        <v>65100</v>
+      </c>
+      <c r="P41" s="3">
         <v>96500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E42" s="3">
         <v>45100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>48300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>70000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>88800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>49600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>52700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>28700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22700</v>
-      </c>
-      <c r="L42" s="3">
-        <v>100</v>
       </c>
       <c r="M42" s="3">
         <v>100</v>
@@ -2075,194 +2164,209 @@
         <v>100</v>
       </c>
       <c r="O42" s="3">
+        <v>100</v>
+      </c>
+      <c r="P42" s="3">
         <v>900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1700</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E43" s="3">
         <v>412500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>248800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>330000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>201100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>320900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>318800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>247300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>277700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>306100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>355700</v>
       </c>
       <c r="N43" s="3">
         <v>355700</v>
       </c>
       <c r="O43" s="3">
+        <v>355700</v>
+      </c>
+      <c r="P43" s="3">
         <v>255700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>257900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1110600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1089400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1225900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>774400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>728000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1052100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>940000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>945700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>954900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>851000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>779400</v>
       </c>
       <c r="N44" s="3">
         <v>779400</v>
       </c>
       <c r="O44" s="3">
+        <v>779400</v>
+      </c>
+      <c r="P44" s="3">
         <v>595800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>553100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E45" s="3">
         <v>15800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>62800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45700</v>
-      </c>
-      <c r="M45" s="3">
-        <v>88400</v>
       </c>
       <c r="N45" s="3">
         <v>88400</v>
       </c>
       <c r="O45" s="3">
+        <v>88400</v>
+      </c>
+      <c r="P45" s="3">
         <v>31800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39200</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1858700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1687500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1727000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1447200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1544500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1514200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1382900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1307900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1340500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1253600</v>
-      </c>
-      <c r="M46" s="3">
-        <v>1247400</v>
       </c>
       <c r="N46" s="3">
         <v>1247400</v>
       </c>
       <c r="O46" s="3">
+        <v>1247400</v>
+      </c>
+      <c r="P46" s="3">
         <v>980700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>912600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2299,105 +2403,114 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>12100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1268800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1256000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1193100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1077500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>956200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1068500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>990500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1035800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1076900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1044400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>873700</v>
       </c>
       <c r="N48" s="3">
         <v>873700</v>
       </c>
       <c r="O48" s="3">
+        <v>873700</v>
+      </c>
+      <c r="P48" s="3">
         <v>655900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>194200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E49" s="3">
         <v>533100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>501600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>590400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>496500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>611700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>620900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>628200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>556300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>527400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>463800</v>
       </c>
       <c r="N49" s="3">
         <v>463800</v>
       </c>
       <c r="O49" s="3">
+        <v>463800</v>
+      </c>
+      <c r="P49" s="3">
         <v>397600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>480900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2601,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E52" s="3">
         <v>14300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>8100</v>
       </c>
       <c r="N52" s="3">
         <v>8100</v>
       </c>
       <c r="O52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="P52" s="3">
         <v>9400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3715100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3514900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3440200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3136700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3020900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3211100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3004600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2980700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2990100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2834300</v>
-      </c>
-      <c r="M54" s="3">
-        <v>2593000</v>
       </c>
       <c r="N54" s="3">
         <v>2593000</v>
       </c>
       <c r="O54" s="3">
+        <v>2593000</v>
+      </c>
+      <c r="P54" s="3">
         <v>2043700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1896400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,79 +2788,83 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>398300</v>
+      </c>
+      <c r="E57" s="3">
         <v>323400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>380600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>355900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>289900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>348300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>290900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>246400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>232500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>230700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>736000</v>
       </c>
       <c r="N57" s="3">
         <v>736000</v>
       </c>
       <c r="O57" s="3">
+        <v>736000</v>
+      </c>
+      <c r="P57" s="3">
         <v>289400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>256400</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>329300</v>
+      </c>
+      <c r="E58" s="3">
         <v>326700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>190700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>56200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
@@ -2742,195 +2875,210 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E59" s="3">
         <v>60200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>64800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>7300</v>
       </c>
       <c r="N59" s="3">
         <v>7300</v>
       </c>
-      <c r="O59" s="3" t="s">
+      <c r="O59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>837500</v>
+      </c>
+      <c r="E60" s="3">
         <v>724100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>641700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>463600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>359600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>422400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>347000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>258500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>235900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>233200</v>
-      </c>
-      <c r="M60" s="3">
-        <v>368700</v>
       </c>
       <c r="N60" s="3">
         <v>368700</v>
       </c>
       <c r="O60" s="3">
+        <v>368700</v>
+      </c>
+      <c r="P60" s="3">
         <v>289400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>256400</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1335500</v>
+      </c>
+      <c r="E61" s="3">
         <v>768900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>860200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>693800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1066600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>912000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>669000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>630000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>600000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>375000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>157000</v>
       </c>
       <c r="N61" s="3">
         <v>157000</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>181000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E62" s="3">
         <v>11100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>43800</v>
       </c>
       <c r="N62" s="3">
         <v>43800</v>
       </c>
       <c r="O62" s="3">
+        <v>43800</v>
+      </c>
+      <c r="P62" s="3">
         <v>34800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>32700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2258500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1557400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1558100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1217300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1462100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1376600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1068500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>929300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>870500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>645800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>569500</v>
       </c>
       <c r="N66" s="3">
         <v>569500</v>
       </c>
       <c r="O66" s="3">
+        <v>569500</v>
+      </c>
+      <c r="P66" s="3">
         <v>324200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>470100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3262,9 +3429,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1118200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1611200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1590500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1604700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1359100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1628000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1740300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1853500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1903500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2022800</v>
-      </c>
-      <c r="M72" s="3">
-        <v>1885900</v>
       </c>
       <c r="N72" s="3">
         <v>1885900</v>
       </c>
       <c r="O72" s="3">
+        <v>1885900</v>
+      </c>
+      <c r="P72" s="3">
         <v>1583300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1306700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1456700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1957500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1882200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1919400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1558900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1834500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1936100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2051400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2119600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2188400</v>
-      </c>
-      <c r="M76" s="3">
-        <v>2023500</v>
       </c>
       <c r="N76" s="3">
         <v>2023500</v>
       </c>
       <c r="O76" s="3">
+        <v>2023500</v>
+      </c>
+      <c r="P76" s="3">
         <v>1719400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1426300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43828</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43464</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42736</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42372</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42281</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41917</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41546</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41182</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E81" s="3">
         <v>533600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>541500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>607200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-225300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>259800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>350800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>362300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>346600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>304900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>237300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>359600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>320200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>148500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E83" s="3">
         <v>107800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>105800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>117300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>126800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>134300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>130700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>136600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>140600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>146400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>116600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>95600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>95300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>94600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>501400</v>
+      </c>
+      <c r="E89" s="3">
         <v>546600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>413500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>617500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>415000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>361000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>538500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>613400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>537900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>353600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>219800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>264100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>427200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>219600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-145300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-203300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-239100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-127500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-50700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-128700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-107700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-92000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-129400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-319400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-284000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-286600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-162600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-76800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-112100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-154900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-182400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-187800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-135800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-110900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-210000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-303400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-425300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-390700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-389500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-172100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-162000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,53 +4457,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E96" s="3">
         <v>131800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>123800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>90500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>30600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>110300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>94600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>84800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-74400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-79700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-63700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-53200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-43700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,142 +4646,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-379400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-452800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-258300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-754800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>83500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-207800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-433200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-389300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-246300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>59400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>154800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>93700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-228300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69100</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-60800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-326000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>441100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-32200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>27000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>GIL</t>
   </si>
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44563</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43828</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43464</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42736</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42372</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41917</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41546</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41182</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3619200</v>
+      </c>
+      <c r="E8" s="3">
         <v>3270600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3195900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3240500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2922600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1981300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2823900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2908600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2750800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2585100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2959200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2415500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2360000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2184300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1948300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2454000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2266900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2319000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2281000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2092400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1788000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2083400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2102600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1949600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1865400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2229100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1830100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1701300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1550300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1552100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1165300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1003700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>877000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>959500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>830200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>193300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>740500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>806000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>801200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>719700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>730100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>585300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>658700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>634000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>396100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,8 +903,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,9 +951,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,87 +1002,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E14" s="3">
         <v>77400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-91000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>29900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-133200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>86300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>83300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>34200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15100</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E15" s="3">
         <v>118900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>102700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>104800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>116200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>126400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>138300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>153600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>157300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1082,9 +1104,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2840500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2575000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2643000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2607200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2403900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2075800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2451600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2471200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2326900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2213500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2632000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2158900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1990600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1841600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1793100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>778700</v>
+      </c>
+      <c r="E18" s="3">
         <v>695600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>552900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>633300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>518700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-94500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>372300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>437400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>423900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>371500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>327200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>256600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>369400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>342700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>155100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1216,248 +1248,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E20" s="3">
         <v>18700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>22500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>867900</v>
+      </c>
+      <c r="E21" s="3">
         <v>795800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>633100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>729800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>625200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>503500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>585000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>574500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>505000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>464500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>364500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>464200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>429900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>246000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>117800</v>
+      </c>
+      <c r="E22" s="3">
         <v>85500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>32100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7300</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>471200</v>
+      </c>
+      <c r="E23" s="3">
         <v>514100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>564200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>566400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>624600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-229400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>249800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>372100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>376800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>351800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>309400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>241200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>366500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>330700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>144100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E24" s="3">
         <v>113200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>393900</v>
+      </c>
+      <c r="E26" s="3">
         <v>400900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>533600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>541500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>607200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-225300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>259800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>350800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>362300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>346600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>304900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>237300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>359600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>320200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>148500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E27" s="3">
         <v>400900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>533600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>541500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>607200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-225300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>259800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>350800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>362300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>346600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>304900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>237300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>359600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>320200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>148500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1647,14 +1704,17 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1695,9 +1755,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,105 +1857,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-22500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E33" s="3">
         <v>400900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>533600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>541500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>607200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-225300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>259800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>350800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>362300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>346600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>304900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>237300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>359600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>320200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>148500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E35" s="3">
         <v>400900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>533600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>541500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>607200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-225300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>259800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>350800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>362300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>346600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>304900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>237300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>359600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>320200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>148500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44563</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43828</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43464</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42736</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42372</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41917</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41546</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41182</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,88 +2162,92 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>284500</v>
+      </c>
+      <c r="E41" s="3">
         <v>98800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>150400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>179200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>505300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50700</v>
-      </c>
-      <c r="N41" s="3">
-        <v>65100</v>
       </c>
       <c r="O41" s="3">
         <v>65100</v>
       </c>
       <c r="P41" s="3">
+        <v>65100</v>
+      </c>
+      <c r="Q41" s="3">
         <v>96500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E42" s="3">
         <v>56800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>45100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>70000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>88800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>49600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>52700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>22700</v>
-      </c>
-      <c r="M42" s="3">
-        <v>100</v>
       </c>
       <c r="N42" s="3">
         <v>100</v>
@@ -2167,206 +2256,221 @@
         <v>100</v>
       </c>
       <c r="P42" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q42" s="3">
         <v>900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1700</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>955700</v>
+      </c>
+      <c r="E43" s="3">
         <v>542400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>412500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>248800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>330000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>201100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>320900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>318800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>247300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>277700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>306100</v>
-      </c>
-      <c r="N43" s="3">
-        <v>355700</v>
       </c>
       <c r="O43" s="3">
         <v>355700</v>
       </c>
       <c r="P43" s="3">
+        <v>355700</v>
+      </c>
+      <c r="Q43" s="3">
         <v>255700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>257900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2370200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1110600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1089400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1225900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>774400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>728000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1052100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>940000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>945700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>954900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>851000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>779400</v>
       </c>
       <c r="O44" s="3">
         <v>779400</v>
       </c>
       <c r="P44" s="3">
+        <v>779400</v>
+      </c>
+      <c r="Q44" s="3">
         <v>595800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>553100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>962800</v>
+      </c>
+      <c r="E45" s="3">
         <v>12100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>62800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45700</v>
-      </c>
-      <c r="N45" s="3">
-        <v>88400</v>
       </c>
       <c r="O45" s="3">
         <v>88400</v>
       </c>
       <c r="P45" s="3">
+        <v>88400</v>
+      </c>
+      <c r="Q45" s="3">
         <v>31800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39200</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4709900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1858700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1687500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1727000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1447200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1544500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1514200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1382900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1307900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1340500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1253600</v>
-      </c>
-      <c r="N46" s="3">
-        <v>1247400</v>
       </c>
       <c r="O46" s="3">
         <v>1247400</v>
       </c>
       <c r="P46" s="3">
+        <v>1247400</v>
+      </c>
+      <c r="Q46" s="3">
         <v>980700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>912600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2406,111 +2510,120 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>12100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1702500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1268800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1256000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1193100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1077500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>956200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1068500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>990500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1035800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1076900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1044400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>873700</v>
       </c>
       <c r="O48" s="3">
         <v>873700</v>
       </c>
       <c r="P48" s="3">
+        <v>873700</v>
+      </c>
+      <c r="Q48" s="3">
         <v>655900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>194200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3890300</v>
+      </c>
+      <c r="E49" s="3">
         <v>525000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>533100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>501600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>590400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>496500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>611700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>620900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>628200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>556300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>527400</v>
-      </c>
-      <c r="N49" s="3">
-        <v>463800</v>
       </c>
       <c r="O49" s="3">
         <v>463800</v>
       </c>
       <c r="P49" s="3">
+        <v>463800</v>
+      </c>
+      <c r="Q49" s="3">
         <v>397600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>480900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,57 +2720,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E52" s="3">
         <v>40800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>8100</v>
       </c>
       <c r="O52" s="3">
         <v>8100</v>
       </c>
       <c r="P52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>9400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18800</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10465200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3715100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3514900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3440200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3136700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3020900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3211100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3004600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2980700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2990100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2834300</v>
-      </c>
-      <c r="N54" s="3">
-        <v>2593000</v>
       </c>
       <c r="O54" s="3">
         <v>2593000</v>
       </c>
       <c r="P54" s="3">
+        <v>2593000</v>
+      </c>
+      <c r="Q54" s="3">
         <v>2043700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1896400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,85 +2918,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1020400</v>
+      </c>
+      <c r="E57" s="3">
         <v>398300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>323400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>380600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>355900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>289900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>348300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>290900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>246400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>232500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>230700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>736000</v>
       </c>
       <c r="O57" s="3">
         <v>736000</v>
       </c>
       <c r="P57" s="3">
+        <v>736000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>289400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>256400</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>587900</v>
+      </c>
+      <c r="E58" s="3">
         <v>329300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>326700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>190700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>29400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>54400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>56200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>33500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -2878,207 +3011,222 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>606300</v>
+      </c>
+      <c r="E59" s="3">
         <v>91000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>60200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>64800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2500</v>
-      </c>
-      <c r="N59" s="3">
-        <v>7300</v>
       </c>
       <c r="O59" s="3">
         <v>7300</v>
       </c>
-      <c r="P59" s="3" t="s">
+      <c r="P59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2235700</v>
+      </c>
+      <c r="E60" s="3">
         <v>837500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>724100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>641700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>463600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>359600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>422400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>347000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>258500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>235900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>233200</v>
-      </c>
-      <c r="N60" s="3">
-        <v>368700</v>
       </c>
       <c r="O60" s="3">
         <v>368700</v>
       </c>
       <c r="P60" s="3">
+        <v>368700</v>
+      </c>
+      <c r="Q60" s="3">
         <v>289400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>256400</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4118400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1335500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>768900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>860200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>693800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1066600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>912000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>669000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>630000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>600000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>375000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>157000</v>
       </c>
       <c r="O61" s="3">
         <v>157000</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>181000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E62" s="3">
         <v>19100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>43800</v>
       </c>
       <c r="O62" s="3">
         <v>43800</v>
       </c>
       <c r="P62" s="3">
+        <v>43800</v>
+      </c>
+      <c r="Q62" s="3">
         <v>34800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>32700</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6903000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2258500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1557400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1558100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1217300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1462100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1376600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1068500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>929300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>870500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>645800</v>
-      </c>
-      <c r="N66" s="3">
-        <v>569500</v>
       </c>
       <c r="O66" s="3">
         <v>569500</v>
       </c>
       <c r="P66" s="3">
+        <v>569500</v>
+      </c>
+      <c r="Q66" s="3">
         <v>324200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>470100</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1170300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1118200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1611200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1590500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1604700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1359100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1628000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1740300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1853500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1903500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2022800</v>
-      </c>
-      <c r="N72" s="3">
-        <v>1885900</v>
       </c>
       <c r="O72" s="3">
         <v>1885900</v>
       </c>
       <c r="P72" s="3">
+        <v>1885900</v>
+      </c>
+      <c r="Q72" s="3">
         <v>1583300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1306700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3562200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1456700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1957500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1882200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1919400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1558900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1834500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1936100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2051400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2119600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2188400</v>
-      </c>
-      <c r="N76" s="3">
-        <v>2023500</v>
       </c>
       <c r="O76" s="3">
         <v>2023500</v>
       </c>
       <c r="P76" s="3">
+        <v>2023500</v>
+      </c>
+      <c r="Q76" s="3">
         <v>1719400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1426300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44563</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43828</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43464</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42736</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42372</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41917</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41546</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41182</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E81" s="3">
         <v>400900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>533600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>541500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>607200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-225300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>259800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>350800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>362300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>346600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>304900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>237300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>359600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>320200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>148500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E83" s="3">
         <v>125000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>107800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>105800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>117300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>126800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>134300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>130700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>136600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>140600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>146400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>116600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>95600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>95300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>94600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>606300</v>
+      </c>
+      <c r="E89" s="3">
         <v>501400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>546600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>413500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>617500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>415000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>361000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>538500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>613400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>537900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>353600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>219800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>264100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>427200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>219600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-106400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-145300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-203300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-239100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-127500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-50700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-128700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-107700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-92000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-129400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-319400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-284000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-286600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-162600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-76800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-112100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-154900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-182400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-187800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-135800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-110900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-210000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-303400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-425300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-390700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-389500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-172100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-162000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,56 +4690,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E96" s="3">
         <v>133500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>131800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>123800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>90500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>30600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>110300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>94600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>84800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-74400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-79700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-63700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-53200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-36600</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,151 +4891,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-177100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-379400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-452800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-258300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-754800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>83500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-207800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-433200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-389300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-246300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>59400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>154800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>93700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-228300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-69100</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E102" s="3">
         <v>9200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-60800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-326000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>441100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-32200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>27000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
